--- a/reports/2026-10-16/public_scholarships_report_2026-10-16.xlsx
+++ b/reports/2026-10-16/public_scholarships_report_2026-10-16.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Report Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'International'!$A$1:$R$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Watchlist (Awaiting Call)'!$A$1:$R$2</definedName>
   </definedNames>
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -127,9 +127,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -498,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -796,7 +793,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0006</t>
+          <t>SCH-202610-0022</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -886,7 +883,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0007</t>
+          <t>SCH-202610-0023</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -976,7 +973,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0009</t>
+          <t>SCH-202610-0025</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1066,7 +1063,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0008</t>
+          <t>SCH-202610-0024</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1248,7 +1245,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0010</t>
+          <t>SCH-202610-0026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1337,8 +1334,742 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0018</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Government of Pakistan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>MS and PhD</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://eportal.hec.gov.pk/idps75</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0008</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CM Foreign Scholarship</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0017</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister Foreign Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>selected universities in the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>merit cum in-affordability basis</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister's Free Laptop Distribution Scheme</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education, Archives and Libraries Department</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>approved universities/colleges</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100% merit-based distribution, high-achieving and deserving enrolled students</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/student/laptop</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0019</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Development Programme for Pakistani Universities</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission, Pakistan</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>HEC recognized universities/DAIs</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0009</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KP Youth Scholarship</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>good academic merit</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0007</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Merit Cum Inaffordability Scholarship</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-305</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>approved list of Educational Institutions (Available on official website) within Pakistan</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>BS &amp; MS</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Student must have scored at least 70% marks in the last attended examination or 3.00 CGPA in each semester, in case of arts specialized university selection will be on the basis of merit aptitude test where selection is on the basis of skills.</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Rs: 160,000/- per month</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/merit_cum_inaffordability</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye Scholarships</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye Scholarships (YTB)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6.500 TL at Associate's and Bachelor's levels, 9.500 TL at Master's level and 13.000 TL at PhD level per month.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>prestigious universities in Türkiye</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>associate, bachelor's, master’s, PhD and research degrees</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>The scholarship program is competitive and merit-based, with a strong emphasis on candidates’ academic excellence</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://tbbs.turkiyeburslari.gov.tr</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://turkiyeburslari.gov.tr/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R9"/>
+  <autoFilter ref="A1:R17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1349,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1647,7 +2378,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0006</t>
+          <t>SCH-202610-0022</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1737,7 +2468,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0007</t>
+          <t>SCH-202610-0023</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1916,8 +2647,742 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0018</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Government of Pakistan</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>MS and PhD</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>https://eportal.hec.gov.pk/idps75</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0008</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CM Foreign Scholarship</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0017</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister Foreign Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>selected universities in the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>merit cum in-affordability basis</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0012</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister's Free Laptop Distribution Scheme</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education, Archives and Libraries Department</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>approved universities/colleges</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100% merit-based distribution, high-achieving and deserving enrolled students</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/student/laptop</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0019</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Development Programme for Pakistani Universities</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission, Pakistan</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>HEC recognized universities/DAIs</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>KP Youth Scholarship</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>good academic merit</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0007</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Merit Cum Inaffordability Scholarship</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-305</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>approved list of Educational Institutions (Available on official website) within Pakistan</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>BS &amp; MS</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Student must have scored at least 70% marks in the last attended examination or 3.00 CGPA in each semester, in case of arts specialized university selection will be on the basis of merit aptitude test where selection is on the basis of skills.</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Rs: 160,000/- per month</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/merit_cum_inaffordability</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0014</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye Scholarships</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye Scholarships (YTB)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6.500 TL at Associate's and Bachelor's levels, 9.500 TL at Master's level and 13.000 TL at PhD level per month.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>prestigious universities in Türkiye</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>associate, bachelor's, master’s, PhD and research degrees</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>The scholarship program is competitive and merit-based, with a strong emphasis on candidates’ academic excellence</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://tbbs.turkiyeburslari.gov.tr</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://turkiyeburslari.gov.tr/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R6"/>
+  <autoFilter ref="A1:R14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2136,17 +3601,17 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0011</t>
+          <t>SCH-202610-0016</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fulbright Foreign Student Program (USEFP Pakistan) 2027</t>
+          <t>Commonwealth Scholarship Programme (Master’s &amp; PhD)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>United States Educational Foundation in Pakistan (USEFP)</t>
+          <t>Commonwealth / Higher Education Commission Pakistan</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2154,52 +3619,54 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Fully funded: Tuition, textbooks, airfare, living stipend, health insurance, visa sponsorship</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Accredited Universities in the United States</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Master's (2 years) and PhD (4-5 years)</t>
+          <t>Master’s &amp; PhD</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Strong academic record and competitive GRE score</t>
+          <t>HEC accepts valid test score of HAT</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -2209,7 +3676,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://usefp.org/scholarships/fulbright-degree.cfm</t>
+          <t>https://www.hec.gov.pk/english/HECAnnouncements/Pages/CW-Scholarship.aspx</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -2219,7 +3686,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>https://usefp.org/</t>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/lao/Pages/default.aspx</t>
         </is>
       </c>
     </row>
@@ -2235,7 +3702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2350,6 +3817,96 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0021</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Global Undergraduate Exchange Program (Global UGRAD)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Bureau of Educational and Cultural Affairs (ECA) of the United States Department of State</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-751</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>colleges or universities in Pakistan and universities across the United States</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>academic merit, leadership potential, and cultural adaptability</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/global-ugrad.cfm</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/global-ugrad.cfm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2370,7 +3927,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Report Title</t>
         </is>
@@ -2382,7 +3939,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Audience</t>
         </is>
@@ -2394,31 +3951,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Last Checked (PKT)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:14 PKT</t>
+          <t>2026-10-16 19:42 PKT</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Run ID</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261016-091400</t>
+          <t>RUN-20261016-194227</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Sources Checked</t>
         </is>
@@ -2428,27 +3985,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Total Opportunities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>New Since Yesterday</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Closing in ≤ 7 Days</t>
         </is>
@@ -2458,27 +4015,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Charsadda District Eligible</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>KP Domicile Eligible</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Broken Links Flagged</t>
         </is>
@@ -2488,7 +4045,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Degraded Mode Active</t>
         </is>

--- a/reports/2026-10-16/public_scholarships_report_2026-10-16.xlsx
+++ b/reports/2026-10-16/public_scholarships_report_2026-10-16.xlsx
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 19:42 PKT</t>
+          <t>2026-10-16 19:53 PKT</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261016-194227</t>
+          <t>RUN-20261016-195337</t>
         </is>
       </c>
     </row>
